--- a/漢字（かんじ）/y.xlsx
+++ b/漢字（かんじ）/y.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="116">
   <si>
     <t>仮名</t>
   </si>
@@ -343,7 +343,11 @@
     <t>預金｜よきん</t>
   </si>
   <si>
-    <t>よる</t>
+    <t>浴</t>
+  </si>
+  <si>
+    <t>浴室｜よくしつ
+海水浴｜かいすいよく</t>
   </si>
   <si>
     <t>よう</t>
@@ -356,6 +360,15 @@
 模様｜もよう</t>
   </si>
   <si>
+    <t>よる</t>
+  </si>
+  <si>
+    <t>幼</t>
+  </si>
+  <si>
+    <t>幼児｜ようじ</t>
+  </si>
+  <si>
     <t>よみ</t>
   </si>
   <si>
@@ -363,12 +376,6 @@
   </si>
   <si>
     <t>読売｜よみうり</t>
-  </si>
-  <si>
-    <t>幼</t>
-  </si>
-  <si>
-    <t>幼児｜ようじ</t>
   </si>
   <si>
     <t>養</t>
@@ -415,6 +422,7 @@
 用意｜ようい
 雇用｜こうよう
 用心｜ようじん
+用心深い｜ようじんぶかい
 代用｜だいよう
 用途｜ようと</t>
   </si>
@@ -1073,12 +1081,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1591,7 +1596,7 @@
       <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1611,36 +1616,36 @@
       <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="31.2" spans="1:7">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1875,7 +1880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" ht="36" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -1886,126 +1891,135 @@
         <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
+      <c r="G5" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>94</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" ht="90" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" ht="90" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" ht="33.6" customHeight="1" spans="1:7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" ht="216" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" ht="21.6" customHeight="1" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" ht="59.4" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>25</v>
@@ -2013,24 +2027,24 @@
     </row>
     <row r="16" ht="54" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" ht="36" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
